--- a/04_Test Cases/PlaceOrder_Test_Cases.xlsx
+++ b/04_Test Cases/PlaceOrder_Test_Cases.xlsx
@@ -558,7 +558,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>09-03-2026</t>
+          <t>05-03-2026</t>
         </is>
       </c>
     </row>
